--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Tabela_Slide.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Tabela_Slide.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB37B6EF-2274-456B-B9AE-B5263104C44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A9FF45-5017-4B56-AE90-E6332D7F9CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Escolaridade" sheetId="2" r:id="rId1"/>
@@ -24,8 +24,11 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">Idade!$A$11:$A$14</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Idade!$B$11:$B$14</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Idade!$A$11:$A$14</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Idade!$B$11:$B$14</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Amostra!$B$3:$B$33</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Amostra!$F$3:$F$33</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Amostra!$C$3:$C$33</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Amostra!$F$3:$F$33</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Amostra!$E$3:$E$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -52,8 +55,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="50">
   <si>
     <t>Idade</t>
   </si>
@@ -153,6 +178,57 @@
   <si>
     <t>fac</t>
   </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Moda</t>
+  </si>
+  <si>
+    <t>Mediana</t>
+  </si>
+  <si>
+    <t>Tempo.S</t>
+  </si>
+  <si>
+    <t>Salário</t>
+  </si>
+  <si>
+    <t>Variância</t>
+  </si>
+  <si>
+    <t>Desvio Padrão</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Minímo</t>
+  </si>
+  <si>
+    <t>Máximo</t>
+  </si>
+  <si>
+    <t>Minimo</t>
+  </si>
+  <si>
+    <t>Mínimo</t>
+  </si>
+  <si>
+    <t>Escor R$ 72500,00</t>
+  </si>
+  <si>
+    <t>outlier</t>
+  </si>
 </sst>
 </file>
 
@@ -187,7 +263,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,8 +282,38 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -244,12 +350,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -296,27 +417,37 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -507,6 +638,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C3C3-44F3-9E9D-A0CF078843D9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -551,6 +687,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-C3C3-44F3-9E9D-A0CF078843D9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -595,6 +736,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-C3C3-44F3-9E9D-A0CF078843D9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1431,6 +1577,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-B424-4BE7-B685-DDC0DC9AB387}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1446,6 +1597,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-B424-4BE7-B685-DDC0DC9AB387}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2823,10 +2979,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.2</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2891,7 +3047,427 @@
 </cx:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Idade</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Idade</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{32C8419E-7D36-4AB7-9F8C-65822A173D88}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.4</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Tempo de Serviço (anos)</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Tempo de Serviço (anos)</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{3DFAE7E3-64E1-4376-8C0E-2D9C72274BB8}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.6</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Salário</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Salário</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{8A4B672D-77AF-486D-A553-345DD875A63B}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx5.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Numero de Dependentes</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Numero de Dependentes</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{BF0B8CDC-5A7D-4CC6-B7B7-4EBC0E79CFE3}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3760,6 +4336,2066 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -8236,6 +10872,323 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>757512</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>65167</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>627946</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>82357</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1BBA724-D8D5-5E3E-03B7-BF528A9514D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="757512" y="5998248"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>616399</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>33098</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>486833</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>50288</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Gráfico 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1379AF96-C3E2-A424-C3C8-DA2574F7DC57}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="616399" y="9012896"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635641</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>77994</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>506075</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>95184</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Gráfico 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8034397C-C6F9-3CF1-44E7-22691EC76B68}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="635641" y="11944156"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>347004</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>90823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>217438</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>108013</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Gráfico 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{729200DE-DC1C-AF09-18D5-1679BFD3FF0F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="347004" y="15003702"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aluno" refreshedDate="46085.427502199076" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="31" xr:uid="{A2B73140-8161-47D7-9788-5935AD568286}">
   <cacheSource type="worksheet">
@@ -10114,14 +13067,14 @@
     <dataField name="Frequência Acumulada" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="23">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
@@ -10199,7 +13152,7 @@
     <dataField name="Frequência Acumulada" fld="5" subtotal="count" showDataAs="runTotal" baseField="5" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="21">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10208,14 +13161,14 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
@@ -10301,7 +13254,7 @@
     <dataField name="Frequência Acumulada" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="18">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10310,14 +13263,14 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
@@ -10407,17 +13360,17 @@
     <dataField name="Frequência Acumulada" fld="4" subtotal="count" showDataAs="runTotal" baseField="4" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="15">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10507,7 +13460,7 @@
     <dataField name="fac" fld="0" subtotal="count" showDataAs="runTotal" baseField="0" baseItem="1"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="12">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="4">
@@ -10519,10 +13472,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="5">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10531,10 +13484,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -10545,7 +13498,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -10637,10 +13590,10 @@
     <dataField name="fac" fld="3" subtotal="count" showDataAs="runTotal" baseField="3" baseItem="1"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="7">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -11762,7 +14715,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K40"/>
+  <dimension ref="A2:Q107"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -11770,13 +14723,16 @@
     <col min="4" max="4" width="11.81640625" customWidth="1"/>
     <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="8" width="10.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="16.7265625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="8.26953125" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" customWidth="1"/>
+    <col min="15" max="15" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="50.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" ht="50.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -11798,7 +14754,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
         <v>40</v>
       </c>
@@ -11818,7 +14774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>25</v>
       </c>
@@ -11837,8 +14793,26 @@
       <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="L4" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="27" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>32</v>
       </c>
@@ -11858,8 +14832,35 @@
         <v>8</v>
       </c>
       <c r="J5" s="2"/>
+      <c r="K5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="22">
+        <f>AVERAGE(C3:C33)</f>
+        <v>2.064516129032258</v>
+      </c>
+      <c r="M5" s="21" cm="1">
+        <f t="array" ref="M5">_xlfn.MODE.MULT(C3:C33)</f>
+        <v>2</v>
+      </c>
+      <c r="N5" s="21">
+        <f>MEDIAN(C3:C33)</f>
+        <v>2</v>
+      </c>
+      <c r="O5" s="22">
+        <f>_xlfn.VAR.S(C3:C33)</f>
+        <v>0.86236559139784963</v>
+      </c>
+      <c r="P5" s="22">
+        <f>_xlfn.STDEV.S(C3:C33)</f>
+        <v>0.92863641507203976</v>
+      </c>
+      <c r="Q5" s="22">
+        <f>P5/L5 *100</f>
+        <v>44.980826355051931</v>
+      </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>30</v>
       </c>
@@ -11879,8 +14880,35 @@
         <v>8</v>
       </c>
       <c r="J6" s="2"/>
+      <c r="K6" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="22">
+        <f>AVERAGE(E3:E33)</f>
+        <v>3115.8709677419356</v>
+      </c>
+      <c r="M6" s="21" cm="1">
+        <f t="array" ref="M6">_xlfn.MODE.MULT(E3:E33)</f>
+        <v>1621</v>
+      </c>
+      <c r="N6" s="22">
+        <f>MEDIAN(E3:E33)</f>
+        <v>2800</v>
+      </c>
+      <c r="O6" s="22">
+        <f>_xlfn.VAR.S(E3:E33)</f>
+        <v>2277568.9827956995</v>
+      </c>
+      <c r="P6" s="22">
+        <f>_xlfn.STDEV.S(E3:E33)</f>
+        <v>1509.161682125444</v>
+      </c>
+      <c r="Q6" s="22">
+        <f>P6/L6 * 100</f>
+        <v>48.434665547756303</v>
+      </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
         <v>34</v>
       </c>
@@ -11900,8 +14928,35 @@
         <v>8</v>
       </c>
       <c r="J7" s="2"/>
+      <c r="K7" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="22">
+        <f>AVERAGE(F3:F33)</f>
+        <v>1.2903225806451613</v>
+      </c>
+      <c r="M7" s="21" cm="1">
+        <f t="array" ref="M7">_xlfn.MODE.MULT(F3:F33)</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="21">
+        <f>MEDIAN(F3:F33)</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="22">
+        <f>_xlfn.VAR.S(F3:F33)</f>
+        <v>1.2129032258064518</v>
+      </c>
+      <c r="P7" s="22">
+        <f>_xlfn.STDEV.S(F3:F33)</f>
+        <v>1.1013188574642911</v>
+      </c>
+      <c r="Q7" s="22">
+        <f>P7/L7 * 100</f>
+        <v>85.352211453482568</v>
+      </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>20</v>
       </c>
@@ -11921,8 +14976,35 @@
         <v>9</v>
       </c>
       <c r="J8" s="2"/>
+      <c r="K8" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="22">
+        <f>AVERAGE(B3:B33)</f>
+        <v>31.29032258064516</v>
+      </c>
+      <c r="M8" s="21" cm="1">
+        <f t="array" ref="M8:M10">_xlfn.MODE.MULT(B3:B33)</f>
+        <v>25</v>
+      </c>
+      <c r="N8" s="21">
+        <f>MEDIAN(B3:B33)</f>
+        <v>30</v>
+      </c>
+      <c r="O8" s="22">
+        <f>_xlfn.VAR.S(B3:B33)</f>
+        <v>85.812903225806437</v>
+      </c>
+      <c r="P8" s="22">
+        <f>_xlfn.STDEV.S(B3:B33)</f>
+        <v>9.2635254210158262</v>
+      </c>
+      <c r="Q8" s="22">
+        <f>P8/L8 * 100</f>
+        <v>29.605081242421715</v>
+      </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>22</v>
       </c>
@@ -11942,8 +15024,13 @@
         <v>9</v>
       </c>
       <c r="J9" s="2"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="21">
+        <v>30</v>
+      </c>
+      <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>21</v>
       </c>
@@ -11962,8 +15049,14 @@
       <c r="G10" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="21">
+        <v>27</v>
+      </c>
+      <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>31</v>
       </c>
@@ -11983,7 +15076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>18</v>
       </c>
@@ -12003,7 +15096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>30</v>
       </c>
@@ -12023,7 +15116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="3">
         <v>41</v>
       </c>
@@ -12043,7 +15136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
         <v>36</v>
       </c>
@@ -12063,7 +15156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="3">
         <v>27</v>
       </c>
@@ -12409,7 +15502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
         <v>30</v>
       </c>
@@ -12429,30 +15522,202 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
+      <c r="H36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="21">
+        <v>18</v>
+      </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
+      <c r="H37" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" s="21">
+        <v>24</v>
+      </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
+      <c r="H38" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" s="21">
+        <v>30</v>
+      </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
+      <c r="H39" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="21">
+        <v>37</v>
+      </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
+      <c r="H40" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I40" s="21">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H42" s="28"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+    </row>
+    <row r="66" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H66" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I66" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I67" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H68" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I68" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H69" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I69" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H70" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I70" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H73" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="I73" s="21">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="74" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H74" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I74" s="21">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="75" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H75" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I75" s="21">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="76" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H76" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I76" s="21">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="77" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H77" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I77" s="21">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="79" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H79" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="I79" s="20">
+        <f>STANDARDIZE(I77,L6,P6)</f>
+        <v>2.7393546239762192</v>
+      </c>
+      <c r="J79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="103" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H103" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I103" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H104" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I104" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H105" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I105" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H106" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I106" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H107" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I107" s="21">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.49212598499999999" footer="0.49212598499999999"/>
   <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>